--- a/test-exports/customers-2020-01-01-to-2030-01-01.xlsx
+++ b/test-exports/customers-2020-01-01-to-2030-01-01.xlsx
@@ -6,6 +6,9 @@
   <sheets>
     <sheet sheetId="1" name="Customer directory" state="visible" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Customer directory'!$5:$5</definedName>
+  </definedNames>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
@@ -16,7 +19,7 @@
     <t>Customer Directory</t>
   </si>
   <si>
-    <t>2020-01-01 to 2030-01-01 | 5 customers</t>
+    <t>01-01-2020 to 01-01-2030 (India Standard Time) | 5 customers</t>
   </si>
   <si>
     <t>Total customers</t>
@@ -52,31 +55,43 @@
     <t>Outstanding due</t>
   </si>
   <si>
-    <t>0000000000</t>
+    <r>
+      <t>0000000000</t>
+    </r>
   </si>
   <si>
     <t>Walk-in Customer</t>
   </si>
   <si>
-    <t>9529138839</t>
+    <r>
+      <t>9529138839</t>
+    </r>
   </si>
   <si>
     <t>BRUCE</t>
   </si>
   <si>
-    <t>ABC324657G</t>
-  </si>
-  <si>
-    <t>9423232371</t>
+    <r>
+      <t>ABC324657G</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>9423232371</t>
+    </r>
   </si>
   <si>
     <t>Kalyan Abuj</t>
   </si>
   <si>
-    <t>ANUJSFJOQ3</t>
-  </si>
-  <si>
-    <t>9970737444</t>
+    <r>
+      <t>ANUJSFJOQ3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>9970737444</t>
+    </r>
   </si>
   <si>
     <t>ram abuj</t>
@@ -85,13 +100,17 @@
     <t>khanapur</t>
   </si>
   <si>
-    <t>9848355987</t>
+    <r>
+      <t>9848355987</t>
+    </r>
   </si>
   <si>
     <t>Deep Audit Customer</t>
   </si>
   <si>
-    <t>ABCDE9999Z</t>
+    <r>
+      <t>ABCDE9999Z</t>
+    </r>
   </si>
   <si>
     <t>audit@example.com</t>
@@ -104,9 +123,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="₹#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="#,##0;[Red]-#,##0"/>
+    <numFmt numFmtId="165" formatCode="[$₹-en-IN]#,##0.00;[Red]-[$₹-en-IN]#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="dd-mmm-yyyy"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -141,7 +161,7 @@
       <color rgb="FF271A05"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -166,6 +186,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD5A044"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFCF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -193,9 +223,15 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="thin">
+        <color rgb="FFE8E1D8"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE8E1D8"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE8E1D8"/>
+      </top>
       <bottom style="thin">
         <color rgb="FFE8E1D8"/>
       </bottom>
@@ -205,34 +241,52 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -276,7 +330,7 @@
     <tableColumn id="8" name="URD purchases" totalsRowFunction="none"/>
     <tableColumn id="9" name="Outstanding due" totalsRowFunction="none"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -606,7 +660,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I10"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <sheetFormatPr defaultRowHeight="18" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="18" customWidth="1"/>
@@ -615,7 +669,7 @@
     <col min="5" max="5" width="24" customWidth="1"/>
     <col min="6" max="6" width="34" customWidth="1"/>
     <col min="7" max="8" width="12" customWidth="1"/>
-    <col min="9" max="9" width="16" customWidth="1"/>
+    <col min="9" max="9" width="18" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -644,19 +698,23 @@
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="4">
+      <c r="B3" s="3"/>
+      <c r="C3" s="4">
         <v>5</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="4"/>
+      <c r="E3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="5">
-        <v>162237.64</v>
-      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="5">
+        <v>100028.81</v>
+      </c>
+      <c r="H3" s="5"/>
     </row>
     <row r="5" ht="26" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
@@ -687,140 +745,149 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="7">
-        <v>46246.504016203704</v>
+        <v>46246.5</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="9" t="s">
         <v>14</v>
       </c>
       <c r="D6" s="8"/>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="9">
+      <c r="E6" s="9"/>
+      <c r="F6" s="9"/>
+      <c r="G6" s="10">
         <v>0</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="10">
         <v>0</v>
       </c>
-      <c r="I6" s="10">
+      <c r="I6" s="11">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A7" s="7">
-        <v>46246.57373842593</v>
-      </c>
-      <c r="B7" s="8" t="s">
+    <row r="7" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="12">
+        <v>46246.5</v>
+      </c>
+      <c r="B7" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="9">
-        <v>14</v>
-      </c>
-      <c r="H7" s="9">
-        <v>1</v>
-      </c>
-      <c r="I7" s="10">
-        <v>69779.33</v>
+      <c r="E7" s="14"/>
+      <c r="F7" s="14"/>
+      <c r="G7" s="15">
+        <v>18</v>
+      </c>
+      <c r="H7" s="15">
+        <v>2</v>
+      </c>
+      <c r="I7" s="16">
+        <v>7570.499999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
-        <v>46247.43103009259</v>
+        <v>46247.5</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="8" t="s">
+      <c r="C8" s="9" t="s">
         <v>19</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="9">
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="10">
         <v>4</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H8" s="10">
         <v>2</v>
       </c>
-      <c r="I8" s="10">
+      <c r="I8" s="11">
         <v>11896.83</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="7">
-        <v>46259.37869212963</v>
-      </c>
-      <c r="B9" s="8" t="s">
+    <row r="9" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="12">
+        <v>46259.5</v>
+      </c>
+      <c r="B9" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="8" t="s">
+      <c r="C9" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8" t="s">
+      <c r="D9" s="13"/>
+      <c r="E9" s="14"/>
+      <c r="F9" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="G9" s="9">
+      <c r="G9" s="15">
         <v>1</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="15">
         <v>0</v>
       </c>
-      <c r="I9" s="10">
+      <c r="I9" s="16">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" ht="20" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="7">
-        <v>46260.085127314815</v>
+        <v>46260.5</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="C10" s="8" t="s">
+      <c r="C10" s="9" t="s">
         <v>25</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="F10" s="8" t="s">
+      <c r="F10" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="G10" s="9">
+      <c r="G10" s="10">
         <v>1</v>
       </c>
-      <c r="H10" s="9">
+      <c r="H10" s="10">
         <v>0</v>
       </c>
-      <c r="I10" s="10">
+      <c r="I10" s="11">
         <v>80561.48</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A5:I10"/>
-  <mergeCells count="2">
+  <mergeCells count="6">
     <mergeCell ref="A1:I1"/>
     <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
   </mergeCells>
-  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <pageMargins left="0.25" right="0.25" top="0.5" bottom="0.5" header="0.2" footer="0.2"/>
+  <pageSetup paperSize="9" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;LKusum ERP&amp;CConfidential business register&amp;RPage &amp;P of &amp;N</oddFooter>
+    <evenFooter>&amp;LKusum ERP&amp;CConfidential business register&amp;RPage &amp;P of &amp;N</evenFooter>
+  </headerFooter>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>

--- a/test-exports/customers-2020-01-01-to-2030-01-01.xlsx
+++ b/test-exports/customers-2020-01-01-to-2030-01-01.xlsx
@@ -306,34 +306,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" name="KusumExport1" displayName="KusumExport1" ref="A5:I10" totalsRowShown="1" headerRowCount="1">
-  <autoFilter ref="A5:I10">
-    <filterColumn colId="0" hiddenButton="1"/>
-    <filterColumn colId="1" hiddenButton="1"/>
-    <filterColumn colId="2" hiddenButton="1"/>
-    <filterColumn colId="3" hiddenButton="1"/>
-    <filterColumn colId="4" hiddenButton="1"/>
-    <filterColumn colId="5" hiddenButton="1"/>
-    <filterColumn colId="6" hiddenButton="1"/>
-    <filterColumn colId="7" hiddenButton="1"/>
-    <filterColumn colId="8" hiddenButton="1"/>
-  </autoFilter>
-  <tableColumns count="9">
-    <tableColumn id="1" name="Registered date" totalsRowLabel="Total"/>
-    <tableColumn id="2" name="Phone / ID" totalsRowFunction="none"/>
-    <tableColumn id="3" name="Customer name" totalsRowFunction="none"/>
-    <tableColumn id="4" name="PAN no." totalsRowFunction="none"/>
-    <tableColumn id="5" name="Email" totalsRowFunction="none"/>
-    <tableColumn id="6" name="Address" totalsRowFunction="none"/>
-    <tableColumn id="7" name="Total sales" totalsRowFunction="none"/>
-    <tableColumn id="8" name="URD purchases" totalsRowFunction="none"/>
-    <tableColumn id="9" name="Outstanding due" totalsRowFunction="none"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
-</table>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -888,8 +860,5 @@
     <oddFooter>&amp;LKusum ERP&amp;CConfidential business register&amp;RPage &amp;P of &amp;N</oddFooter>
     <evenFooter>&amp;LKusum ERP&amp;CConfidential business register&amp;RPage &amp;P of &amp;N</evenFooter>
   </headerFooter>
-  <tableParts count="1">
-    <tablePart r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>